--- a/output/YASKAWA_NEW_SHIPMENT.xlsx
+++ b/output/YASKAWA_NEW_SHIPMENT.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="O2" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P2" s="53" t="n">
@@ -903,7 +903,7 @@
       </c>
       <c r="O3" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P3" s="53" t="n">
@@ -969,7 +969,7 @@
       </c>
       <c r="O4" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P4" s="53" t="n">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="O5" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P5" s="53" t="n">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="O6" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P6" s="53" t="n">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="O7" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P7" s="53" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="O8" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P8" s="53" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="O9" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P9" s="53" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="O10" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P10" s="53" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="O11" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P11" s="53" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O12" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P12" s="53" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="O13" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P13" s="53" t="n">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="O14" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P14" s="53" t="n">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="O15" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P15" s="53" t="n">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="O16" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P16" s="53" t="n">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="O17" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P17" s="53" t="n">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="O18" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P18" s="53" t="n">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="O19" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P19" s="53" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="O20" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P20" s="53" t="n">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="O21" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P21" s="53" t="n">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O22" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P22" s="53" t="n">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="O23" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P23" s="53" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="O24" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P24" s="53" t="n">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="O25" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P25" s="53" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="O26" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P26" s="53" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="O27" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P27" s="53" t="n">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="O28" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P28" s="53" t="n">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="O29" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P29" s="53" t="n">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O30" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P30" s="53" t="n">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="O31" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P31" s="53" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="O32" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P32" s="53" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O33" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P33" s="53" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O34" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P34" s="53" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="O35" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P35" s="53" t="n">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="O36" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P36" s="53" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="O37" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P37" s="53" t="n">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="O38" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P38" s="53" t="n">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="O39" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P39" s="53" t="n">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="O40" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P40" s="53" t="n">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O41" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P41" s="53" t="n">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="O42" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P42" s="53" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="O43" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P43" s="53" t="n">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="O44" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P44" s="53" t="n">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="O45" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P45" s="53" t="n">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="O46" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P46" s="53" t="n">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O47" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P47" s="53" t="n">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="O48" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P48" s="53" t="n">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O49" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P49" s="53" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O50" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P50" s="53" t="n">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="O51" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P51" s="53" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O52" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P52" s="53" t="n">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="O53" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P53" s="53" t="n">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="O54" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P54" s="53" t="n">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="O55" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P55" s="53" t="n">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="O56" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P56" s="53" t="n">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="O57" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P57" s="53" t="n">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="O58" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P58" s="53" t="n">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="O59" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P59" s="53" t="n">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O60" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P60" s="53" t="n">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="O61" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P61" s="53" t="n">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="O62" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P62" s="53" t="n">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="O63" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P63" s="53" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="O64" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P64" s="53" t="n">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="O65" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P65" s="53" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="O66" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P66" s="53" t="n">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="O67" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P67" s="53" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O68" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P68" s="53" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="O69" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P69" s="53" t="n">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="O70" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P70" s="53" t="n">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="O71" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P71" s="53" t="n">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="O72" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P72" s="53" t="n">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="O73" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P73" s="53" t="n">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="O74" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P74" s="53" t="n">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="O75" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P75" s="53" t="n">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="O76" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P76" s="53" t="n">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="O77" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P77" s="53" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="O78" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P78" s="53" t="n">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="O79" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P79" s="53" t="n">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="O80" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P80" s="53" t="n">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="O81" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P81" s="53" t="n">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="O82" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P82" s="53" t="n">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="O83" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P83" s="53" t="n">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O84" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P84" s="53" t="n">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="O85" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P85" s="53" t="n">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="O86" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P86" s="53" t="n">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O87" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P87" s="53" t="n">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="O88" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P88" s="53" t="n">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="O89" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P89" s="53" t="n">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="O90" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P90" s="53" t="n">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="O91" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P91" s="53" t="n">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="O92" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P92" s="53" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="O93" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P93" s="53" t="n">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="O94" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P94" s="53" t="n">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O95" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P95" s="53" t="n">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="O96" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P96" s="53" t="n">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="O97" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P97" s="53" t="n">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O98" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P98" s="53" t="n">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="O99" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P99" s="53" t="n">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="O100" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P100" s="53" t="n">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="O101" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P101" s="53" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="O102" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P102" s="53" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="O103" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P103" s="53" t="n">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="O104" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P104" s="53" t="n">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="O105" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P105" s="53" t="n">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O106" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P106" s="53" t="n">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="O107" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P107" s="53" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="O108" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P108" s="53" t="n">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="O109" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P109" s="53" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="O110" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P110" s="53" t="n">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="O111" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P111" s="53" t="n">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="O112" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P112" s="53" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="O113" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P113" s="53" t="n">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O114" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P114" s="53" t="n">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="O115" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P115" s="53" t="n">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="O116" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P116" s="53" t="n">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="O117" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P117" s="53" t="n">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="O118" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P118" s="53" t="n">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="O119" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P119" s="53" t="n">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="O120" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P120" s="53" t="n">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="O121" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P121" s="53" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="O122" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P122" s="53" t="n">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="O123" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P123" s="53" t="n">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="O124" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P124" s="53" t="n">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="O125" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P125" s="53" t="n">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="O126" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P126" s="53" t="n">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="O127" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P127" s="53" t="n">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="O128" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P128" s="53" t="n">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="O129" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P129" s="53" t="n">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="O130" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P130" s="53" t="n">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="O131" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P131" s="53" t="n">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="O132" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P132" s="53" t="n">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O133" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P133" s="53" t="n">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="O134" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P134" s="53" t="n">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="O135" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P135" s="53" t="n">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="O136" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P136" s="53" t="n">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="O137" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P137" s="53" t="n">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="O138" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P138" s="53" t="n">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="O139" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P139" s="53" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="O140" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P140" s="53" t="n">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="O141" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P141" s="53" t="n">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="O142" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P142" s="53" t="n">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="O143" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P143" s="53" t="n">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="O144" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P144" s="53" t="n">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="O145" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P145" s="53" t="n">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="O146" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P146" s="53" t="n">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="O147" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P147" s="53" t="n">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="O148" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P148" s="53" t="n">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="O149" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P149" s="53" t="n">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="O150" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P150" s="53" t="n">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="O151" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P151" s="53" t="n">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="O152" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P152" s="53" t="n">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="O153" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P153" s="53" t="n">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="O154" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P154" s="53" t="n">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="O155" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P155" s="53" t="n">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="O156" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P156" s="53" t="n">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="O157" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P157" s="53" t="n">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="O158" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P158" s="53" t="n">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="O159" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P159" s="53" t="n">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="O160" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P160" s="53" t="n">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="O161" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P161" s="53" t="n">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="O162" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P162" s="53" t="n">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="O163" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P163" s="53" t="n">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="O164" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P164" s="53" t="n">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="O165" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P165" s="53" t="n">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="O166" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P166" s="53" t="n">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="O167" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P167" s="53" t="n">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="O168" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P168" s="53" t="n">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="O169" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P169" s="53" t="n">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="O170" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P170" s="53" t="n">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="O171" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P171" s="53" t="n">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="O172" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P172" s="53" t="n">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="O173" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P173" s="53" t="n">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="O174" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P174" s="53" t="n">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="O175" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P175" s="53" t="n">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="O176" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P176" s="53" t="n">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="O177" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P177" s="53" t="n">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="O178" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P178" s="53" t="n">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="O179" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P179" s="53" t="n">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="O180" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P180" s="53" t="n">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="O181" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P181" s="53" t="n">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="O182" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P182" s="53" t="n">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="O183" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P183" s="53" t="n">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="O184" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P184" s="53" t="n">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="O185" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P185" s="53" t="n">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="O186" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P186" s="53" t="n">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="O187" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P187" s="53" t="n">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="O188" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P188" s="53" t="n">
@@ -12443,7 +12443,7 @@
       </c>
       <c r="O189" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P189" s="53" t="n">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="O190" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P190" s="53" t="n">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="O191" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P191" s="53" t="n">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="O192" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P192" s="53" t="n">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="O193" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P193" s="53" t="n">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="O194" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P194" s="53" t="n">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="O195" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P195" s="53" t="n">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="O196" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P196" s="53" t="n">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="O197" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P197" s="53" t="n">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="O198" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P198" s="53" t="n">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="O199" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P199" s="53" t="n">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="O200" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P200" s="53" t="n">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="O201" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P201" s="53" t="n">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="O202" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P202" s="53" t="n">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="O203" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P203" s="53" t="n">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="O204" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P204" s="53" t="n">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="O205" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P205" s="53" t="n">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="O206" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P206" s="53" t="n">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="O207" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P207" s="53" t="n">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="O208" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P208" s="53" t="n">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="O209" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P209" s="53" t="n">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="O210" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P210" s="53" t="n">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="O211" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P211" s="53" t="n">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="O212" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P212" s="53" t="n">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="O213" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P213" s="53" t="n">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="O214" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P214" s="53" t="n">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="O215" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P215" s="53" t="n">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="O216" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P216" s="53" t="n">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="O217" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P217" s="53" t="n">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="O218" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P218" s="53" t="n">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="O219" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P219" s="53" t="n">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="O220" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P220" s="53" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="O221" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P221" s="53" t="n">
@@ -14489,7 +14489,7 @@
       </c>
       <c r="O222" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P222" s="53" t="n">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="O223" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P223" s="53" t="n">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="O224" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P224" s="53" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="O225" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P225" s="53" t="n">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="O226" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P226" s="53" t="n">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="O227" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P227" s="53" t="n">
@@ -14865,7 +14865,7 @@
       </c>
       <c r="O228" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P228" s="53" t="n">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="O229" s="54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P229" s="53" t="n">
@@ -39543,7 +39543,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39560,7 +39560,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39581,7 +39581,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39602,7 +39602,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39619,7 +39619,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39636,7 +39636,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39653,7 +39653,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39670,7 +39670,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39687,7 +39687,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39704,7 +39704,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39721,7 +39721,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39738,7 +39738,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39755,7 +39755,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39772,7 +39772,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39789,7 +39789,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39806,7 +39806,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39823,7 +39823,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39840,7 +39840,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39857,7 +39857,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39874,7 +39874,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39908,7 +39908,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39942,7 +39942,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39959,7 +39959,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39976,7 +39976,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39993,7 +39993,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40010,7 +40010,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40027,7 +40027,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40044,7 +40044,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40061,7 +40061,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40078,7 +40078,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40095,7 +40095,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40112,7 +40112,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40129,7 +40129,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40146,7 +40146,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40163,7 +40163,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40180,7 +40180,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40197,7 +40197,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40214,7 +40214,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40231,7 +40231,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40248,7 +40248,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40265,7 +40265,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40282,7 +40282,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40299,7 +40299,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40316,7 +40316,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40333,7 +40333,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40367,7 +40367,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40384,7 +40384,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40401,7 +40401,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40435,7 +40435,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40452,7 +40452,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40469,7 +40469,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40486,7 +40486,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40503,7 +40503,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40520,7 +40520,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40537,7 +40537,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40554,7 +40554,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40571,7 +40571,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40588,7 +40588,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40605,7 +40605,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40622,7 +40622,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40639,7 +40639,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40656,7 +40656,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40673,7 +40673,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40690,7 +40690,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40707,7 +40707,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40724,7 +40724,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40741,7 +40741,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40758,7 +40758,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40775,7 +40775,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40792,7 +40792,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40809,7 +40809,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40826,7 +40826,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40843,7 +40843,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40860,7 +40860,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40877,7 +40877,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40894,7 +40894,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40911,7 +40911,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40928,7 +40928,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40945,7 +40945,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40962,7 +40962,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40996,7 +40996,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41013,7 +41013,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41030,7 +41030,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41047,7 +41047,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41064,7 +41064,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41081,7 +41081,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41098,7 +41098,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41115,7 +41115,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41132,7 +41132,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41149,7 +41149,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41166,7 +41166,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41183,7 +41183,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41200,7 +41200,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41217,7 +41217,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41251,7 +41251,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41268,7 +41268,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41285,7 +41285,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41302,7 +41302,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41319,7 +41319,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41336,7 +41336,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41353,7 +41353,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41370,7 +41370,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41387,7 +41387,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41404,7 +41404,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41421,7 +41421,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41438,7 +41438,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41455,7 +41455,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41472,7 +41472,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41489,7 +41489,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41506,7 +41506,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41523,7 +41523,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41540,7 +41540,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41557,7 +41557,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41574,7 +41574,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41591,7 +41591,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41608,7 +41608,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41625,7 +41625,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41642,7 +41642,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41659,7 +41659,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41676,7 +41676,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41693,7 +41693,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41710,7 +41710,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41727,7 +41727,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41744,7 +41744,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41761,7 +41761,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41778,7 +41778,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41795,7 +41795,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41812,7 +41812,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41829,7 +41829,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41846,7 +41846,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41863,7 +41863,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41880,7 +41880,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41897,7 +41897,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41914,7 +41914,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41931,7 +41931,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41948,7 +41948,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41982,7 +41982,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41999,7 +41999,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42016,7 +42016,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42033,7 +42033,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42050,7 +42050,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42067,7 +42067,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42084,7 +42084,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42101,7 +42101,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42118,7 +42118,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42135,7 +42135,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42152,7 +42152,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42169,7 +42169,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42186,7 +42186,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42203,7 +42203,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42220,7 +42220,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42237,7 +42237,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42254,7 +42254,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42271,7 +42271,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42288,7 +42288,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42305,7 +42305,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42339,7 +42339,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42356,7 +42356,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42373,7 +42373,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42390,7 +42390,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42407,7 +42407,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42424,7 +42424,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42441,7 +42441,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42458,7 +42458,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42475,7 +42475,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42492,7 +42492,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42509,7 +42509,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42526,7 +42526,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42543,7 +42543,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42560,7 +42560,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42577,7 +42577,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42594,7 +42594,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42611,7 +42611,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42628,7 +42628,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42645,7 +42645,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42662,7 +42662,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42679,7 +42679,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42696,7 +42696,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42713,7 +42713,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42730,7 +42730,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42747,7 +42747,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42764,7 +42764,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42781,7 +42781,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42798,7 +42798,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42815,7 +42815,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42832,7 +42832,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42849,7 +42849,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42866,7 +42866,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42883,7 +42883,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42900,7 +42900,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42917,7 +42917,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42934,7 +42934,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42951,7 +42951,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42968,7 +42968,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42985,7 +42985,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43002,7 +43002,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43019,7 +43019,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43036,7 +43036,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43053,7 +43053,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43070,7 +43070,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43087,7 +43087,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43104,7 +43104,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43121,7 +43121,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43138,7 +43138,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43155,7 +43155,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43172,7 +43172,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43189,7 +43189,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43206,7 +43206,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43223,7 +43223,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43240,7 +43240,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43257,7 +43257,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43274,7 +43274,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43291,7 +43291,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43308,7 +43308,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43325,7 +43325,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43342,7 +43342,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43359,7 +43359,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43376,7 +43376,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43397,7 +43397,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43418,7 +43418,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>

--- a/output/YASKAWA_NEW_SHIPMENT.xlsx
+++ b/output/YASKAWA_NEW_SHIPMENT.xlsx
@@ -818,7 +818,7 @@
       </c>
       <c r="H2" s="54" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="I2" s="54" t="n">
@@ -841,11 +841,11 @@
       </c>
       <c r="O2" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/705</t>
         </is>
       </c>
       <c r="P2" s="53" t="n">
-        <v>46316</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="3">
@@ -880,7 +880,7 @@
       </c>
       <c r="H3" s="54" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="I3" s="54" t="n">
@@ -903,11 +903,11 @@
       </c>
       <c r="O3" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/705</t>
         </is>
       </c>
       <c r="P3" s="53" t="n">
-        <v>46316</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="4">
@@ -969,11 +969,11 @@
       </c>
       <c r="O4" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/708</t>
         </is>
       </c>
       <c r="P4" s="53" t="n">
-        <v>46316</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="5">
@@ -1035,11 +1035,11 @@
       </c>
       <c r="O5" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/708</t>
         </is>
       </c>
       <c r="P5" s="53" t="n">
-        <v>46316</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="6">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H6" s="54" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO000MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="I6" s="54" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="O6" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/710</t>
         </is>
       </c>
       <c r="P6" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="7">
@@ -1159,11 +1159,11 @@
       </c>
       <c r="O7" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P7" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="8">
@@ -1221,11 +1221,11 @@
       </c>
       <c r="O8" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P8" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="9">
@@ -1283,11 +1283,11 @@
       </c>
       <c r="O9" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P9" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="10">
@@ -1345,11 +1345,11 @@
       </c>
       <c r="O10" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P10" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="11">
@@ -1407,11 +1407,11 @@
       </c>
       <c r="O11" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P11" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="12">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="O12" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P12" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="13">
@@ -1531,11 +1531,11 @@
       </c>
       <c r="O13" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P13" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="14">
@@ -1593,11 +1593,11 @@
       </c>
       <c r="O14" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P14" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="15">
@@ -1655,11 +1655,11 @@
       </c>
       <c r="O15" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P15" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="16">
@@ -1717,11 +1717,11 @@
       </c>
       <c r="O16" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P16" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="17">
@@ -1779,11 +1779,11 @@
       </c>
       <c r="O17" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P17" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="18">
@@ -1841,11 +1841,11 @@
       </c>
       <c r="O18" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P18" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="19">
@@ -1903,11 +1903,11 @@
       </c>
       <c r="O19" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P19" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="20">
@@ -1965,11 +1965,11 @@
       </c>
       <c r="O20" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P20" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="21">
@@ -2027,11 +2027,11 @@
       </c>
       <c r="O21" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P21" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="22">
@@ -2089,11 +2089,11 @@
       </c>
       <c r="O22" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P22" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="23">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="O23" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P23" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="24">
@@ -2213,11 +2213,11 @@
       </c>
       <c r="O24" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P24" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="25">
@@ -2275,11 +2275,11 @@
       </c>
       <c r="O25" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P25" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="26">
@@ -2337,11 +2337,11 @@
       </c>
       <c r="O26" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P26" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="27">
@@ -2399,11 +2399,11 @@
       </c>
       <c r="O27" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P27" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="28">
@@ -2461,11 +2461,11 @@
       </c>
       <c r="O28" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P28" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="29">
@@ -2523,11 +2523,11 @@
       </c>
       <c r="O29" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P29" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="30">
@@ -2585,11 +2585,11 @@
       </c>
       <c r="O30" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P30" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="31">
@@ -2647,11 +2647,11 @@
       </c>
       <c r="O31" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P31" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="32">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H32" s="54" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00M00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="I32" s="54" t="n">
@@ -2709,11 +2709,11 @@
       </c>
       <c r="O32" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P32" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="33">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="H33" s="54" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN</t>
+          <t>315-4NE23 - VIPA CPU 315SN</t>
         </is>
       </c>
       <c r="I33" s="54" t="n">
@@ -2771,11 +2771,11 @@
       </c>
       <c r="O33" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/717</t>
         </is>
       </c>
       <c r="P33" s="53" t="n">
-        <v>46316</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="34">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H34" s="54" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN</t>
+          <t>315-4NE23 - VIPA CPU 315SN</t>
         </is>
       </c>
       <c r="I34" s="54" t="n">
@@ -2833,11 +2833,11 @@
       </c>
       <c r="O34" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/717</t>
         </is>
       </c>
       <c r="P34" s="53" t="n">
-        <v>46316</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="35">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="P35" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="36">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="P36" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="37">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="P37" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="38">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="P38" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="39">
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="P39" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="40">
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="P40" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="41">
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="P41" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="42">
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="P42" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="43">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P43" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="44">
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="P44" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="45">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="P45" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="46">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="P46" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="47">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="P47" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="48">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="P48" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="49">
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="P49" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="50">
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="P50" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="51">
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="P51" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="52">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="P52" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="53">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="P53" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="54">
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="P54" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="55">
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="P55" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="56">
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="P56" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="57">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="P57" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="58">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="P58" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="59">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="P59" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="60">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="H60" s="54" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-COO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="I60" s="54" t="n">
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="P60" s="53" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="61">
@@ -4507,11 +4507,11 @@
       </c>
       <c r="O61" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P61" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="62">
@@ -4569,11 +4569,11 @@
       </c>
       <c r="O62" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P62" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="63">
@@ -4631,11 +4631,11 @@
       </c>
       <c r="O63" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P63" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="64">
@@ -4693,11 +4693,11 @@
       </c>
       <c r="O64" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P64" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="65">
@@ -4755,11 +4755,11 @@
       </c>
       <c r="O65" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P65" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="66">
@@ -4817,11 +4817,11 @@
       </c>
       <c r="O66" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P66" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="67">
@@ -4879,11 +4879,11 @@
       </c>
       <c r="O67" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P67" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="68">
@@ -4941,11 +4941,11 @@
       </c>
       <c r="O68" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P68" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="69">
@@ -5003,11 +5003,11 @@
       </c>
       <c r="O69" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P69" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="70">
@@ -5065,11 +5065,11 @@
       </c>
       <c r="O70" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P70" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="71">
@@ -5127,11 +5127,11 @@
       </c>
       <c r="O71" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P71" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="72">
@@ -5189,11 +5189,11 @@
       </c>
       <c r="O72" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P72" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="73">
@@ -5251,11 +5251,11 @@
       </c>
       <c r="O73" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P73" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="74">
@@ -5313,11 +5313,11 @@
       </c>
       <c r="O74" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P74" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="75">
@@ -5375,11 +5375,11 @@
       </c>
       <c r="O75" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P75" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="76">
@@ -5437,11 +5437,11 @@
       </c>
       <c r="O76" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P76" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="77">
@@ -5499,11 +5499,11 @@
       </c>
       <c r="O77" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P77" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="78">
@@ -5561,11 +5561,11 @@
       </c>
       <c r="O78" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P78" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="79">
@@ -5623,11 +5623,11 @@
       </c>
       <c r="O79" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P79" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="80">
@@ -5685,11 +5685,11 @@
       </c>
       <c r="O80" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P80" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="81">
@@ -5747,11 +5747,11 @@
       </c>
       <c r="O81" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P81" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="82">
@@ -5809,11 +5809,11 @@
       </c>
       <c r="O82" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P82" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="83">
@@ -5871,11 +5871,11 @@
       </c>
       <c r="O83" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P83" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="84">
@@ -5933,11 +5933,11 @@
       </c>
       <c r="O84" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P84" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="85">
@@ -5995,11 +5995,11 @@
       </c>
       <c r="O85" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P85" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="86">
@@ -6057,11 +6057,11 @@
       </c>
       <c r="O86" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P86" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="87">
@@ -6119,11 +6119,11 @@
       </c>
       <c r="O87" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P87" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="88">
@@ -6181,11 +6181,11 @@
       </c>
       <c r="O88" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P88" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="89">
@@ -6243,11 +6243,11 @@
       </c>
       <c r="O89" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P89" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="90">
@@ -6305,11 +6305,11 @@
       </c>
       <c r="O90" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P90" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="91">
@@ -6367,11 +6367,11 @@
       </c>
       <c r="O91" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P91" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="92">
@@ -6429,11 +6429,11 @@
       </c>
       <c r="O92" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P92" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="93">
@@ -6491,11 +6491,11 @@
       </c>
       <c r="O93" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P93" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="94">
@@ -6553,11 +6553,11 @@
       </c>
       <c r="O94" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P94" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="95">
@@ -6615,11 +6615,11 @@
       </c>
       <c r="O95" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P95" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="96">
@@ -6677,11 +6677,11 @@
       </c>
       <c r="O96" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P96" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="97">
@@ -6739,11 +6739,11 @@
       </c>
       <c r="O97" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P97" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="98">
@@ -6801,11 +6801,11 @@
       </c>
       <c r="O98" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P98" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="99">
@@ -6863,11 +6863,11 @@
       </c>
       <c r="O99" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P99" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="100">
@@ -6925,11 +6925,11 @@
       </c>
       <c r="O100" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P100" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="101">
@@ -6987,11 +6987,11 @@
       </c>
       <c r="O101" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P101" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="102">
@@ -7049,11 +7049,11 @@
       </c>
       <c r="O102" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P102" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="103">
@@ -7111,11 +7111,11 @@
       </c>
       <c r="O103" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P103" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="104">
@@ -7173,11 +7173,11 @@
       </c>
       <c r="O104" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P104" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="105">
@@ -7235,11 +7235,11 @@
       </c>
       <c r="O105" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P105" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="106">
@@ -7297,11 +7297,11 @@
       </c>
       <c r="O106" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P106" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="107">
@@ -7359,11 +7359,11 @@
       </c>
       <c r="O107" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P107" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="108">
@@ -7421,11 +7421,11 @@
       </c>
       <c r="O108" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P108" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="109">
@@ -7483,11 +7483,11 @@
       </c>
       <c r="O109" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P109" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="110">
@@ -7545,11 +7545,11 @@
       </c>
       <c r="O110" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P110" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="111">
@@ -7607,11 +7607,11 @@
       </c>
       <c r="O111" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P111" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="112">
@@ -7669,11 +7669,11 @@
       </c>
       <c r="O112" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P112" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="113">
@@ -7731,11 +7731,11 @@
       </c>
       <c r="O113" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P113" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="114">
@@ -7793,11 +7793,11 @@
       </c>
       <c r="O114" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P114" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="115">
@@ -7855,11 +7855,11 @@
       </c>
       <c r="O115" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P115" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="116">
@@ -7917,11 +7917,11 @@
       </c>
       <c r="O116" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P116" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="117">
@@ -7979,11 +7979,11 @@
       </c>
       <c r="O117" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P117" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="118">
@@ -8041,11 +8041,11 @@
       </c>
       <c r="O118" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P118" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="119">
@@ -8103,11 +8103,11 @@
       </c>
       <c r="O119" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P119" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="120">
@@ -8165,11 +8165,11 @@
       </c>
       <c r="O120" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P120" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="121">
@@ -8227,11 +8227,11 @@
       </c>
       <c r="O121" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P121" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="122">
@@ -8289,11 +8289,11 @@
       </c>
       <c r="O122" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P122" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="123">
@@ -8351,11 +8351,11 @@
       </c>
       <c r="O123" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P123" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="124">
@@ -8413,11 +8413,11 @@
       </c>
       <c r="O124" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P124" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="125">
@@ -8475,11 +8475,11 @@
       </c>
       <c r="O125" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P125" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="126">
@@ -8537,11 +8537,11 @@
       </c>
       <c r="O126" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P126" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="127">
@@ -8599,11 +8599,11 @@
       </c>
       <c r="O127" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P127" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="128">
@@ -8661,11 +8661,11 @@
       </c>
       <c r="O128" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P128" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="129">
@@ -8723,11 +8723,11 @@
       </c>
       <c r="O129" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P129" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="130">
@@ -8785,11 +8785,11 @@
       </c>
       <c r="O130" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P130" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="131">
@@ -8847,11 +8847,11 @@
       </c>
       <c r="O131" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P131" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="132">
@@ -8909,11 +8909,11 @@
       </c>
       <c r="O132" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P132" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="133">
@@ -8971,11 +8971,11 @@
       </c>
       <c r="O133" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P133" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="134">
@@ -9033,11 +9033,11 @@
       </c>
       <c r="O134" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P134" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="135">
@@ -9095,11 +9095,11 @@
       </c>
       <c r="O135" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P135" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="136">
@@ -9157,11 +9157,11 @@
       </c>
       <c r="O136" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P136" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="137">
@@ -9219,11 +9219,11 @@
       </c>
       <c r="O137" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P137" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="138">
@@ -9281,11 +9281,11 @@
       </c>
       <c r="O138" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P138" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="139">
@@ -9343,11 +9343,11 @@
       </c>
       <c r="O139" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P139" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="140">
@@ -9405,11 +9405,11 @@
       </c>
       <c r="O140" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P140" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="141">
@@ -9467,11 +9467,11 @@
       </c>
       <c r="O141" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P141" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="142">
@@ -9529,11 +9529,11 @@
       </c>
       <c r="O142" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P142" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="143">
@@ -9591,11 +9591,11 @@
       </c>
       <c r="O143" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P143" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="144">
@@ -9653,11 +9653,11 @@
       </c>
       <c r="O144" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P144" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="145">
@@ -9715,11 +9715,11 @@
       </c>
       <c r="O145" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P145" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="146">
@@ -9777,11 +9777,11 @@
       </c>
       <c r="O146" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P146" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="147">
@@ -9839,11 +9839,11 @@
       </c>
       <c r="O147" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P147" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="148">
@@ -9901,11 +9901,11 @@
       </c>
       <c r="O148" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P148" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="149">
@@ -9963,11 +9963,11 @@
       </c>
       <c r="O149" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P149" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="150">
@@ -10025,11 +10025,11 @@
       </c>
       <c r="O150" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P150" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="151">
@@ -10087,11 +10087,11 @@
       </c>
       <c r="O151" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P151" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="152">
@@ -10149,11 +10149,11 @@
       </c>
       <c r="O152" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P152" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="153">
@@ -10211,11 +10211,11 @@
       </c>
       <c r="O153" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P153" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="154">
@@ -10273,11 +10273,11 @@
       </c>
       <c r="O154" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P154" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="155">
@@ -10335,11 +10335,11 @@
       </c>
       <c r="O155" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P155" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="156">
@@ -10397,11 +10397,11 @@
       </c>
       <c r="O156" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P156" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="157">
@@ -10459,11 +10459,11 @@
       </c>
       <c r="O157" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P157" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="158">
@@ -10521,11 +10521,11 @@
       </c>
       <c r="O158" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P158" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="159">
@@ -10583,11 +10583,11 @@
       </c>
       <c r="O159" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P159" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="160">
@@ -10645,11 +10645,11 @@
       </c>
       <c r="O160" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P160" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="161">
@@ -10707,11 +10707,11 @@
       </c>
       <c r="O161" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P161" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="162">
@@ -10769,11 +10769,11 @@
       </c>
       <c r="O162" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P162" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="163">
@@ -10831,11 +10831,11 @@
       </c>
       <c r="O163" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P163" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="164">
@@ -10893,11 +10893,11 @@
       </c>
       <c r="O164" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P164" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="165">
@@ -10955,11 +10955,11 @@
       </c>
       <c r="O165" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P165" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="166">
@@ -11017,11 +11017,11 @@
       </c>
       <c r="O166" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P166" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="167">
@@ -11079,11 +11079,11 @@
       </c>
       <c r="O167" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P167" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="168">
@@ -11141,11 +11141,11 @@
       </c>
       <c r="O168" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P168" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="169">
@@ -11203,11 +11203,11 @@
       </c>
       <c r="O169" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P169" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="170">
@@ -11265,11 +11265,11 @@
       </c>
       <c r="O170" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P170" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="171">
@@ -11327,11 +11327,11 @@
       </c>
       <c r="O171" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P171" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="172">
@@ -11389,11 +11389,11 @@
       </c>
       <c r="O172" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P172" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="173">
@@ -11451,11 +11451,11 @@
       </c>
       <c r="O173" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P173" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="174">
@@ -11513,11 +11513,11 @@
       </c>
       <c r="O174" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P174" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="175">
@@ -11575,11 +11575,11 @@
       </c>
       <c r="O175" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P175" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="176">
@@ -11637,11 +11637,11 @@
       </c>
       <c r="O176" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P176" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="177">
@@ -11699,11 +11699,11 @@
       </c>
       <c r="O177" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P177" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="178">
@@ -11761,11 +11761,11 @@
       </c>
       <c r="O178" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P178" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="179">
@@ -11823,11 +11823,11 @@
       </c>
       <c r="O179" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P179" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="180">
@@ -11885,11 +11885,11 @@
       </c>
       <c r="O180" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P180" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="181">
@@ -11947,11 +11947,11 @@
       </c>
       <c r="O181" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P181" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="182">
@@ -12009,11 +12009,11 @@
       </c>
       <c r="O182" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P182" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="183">
@@ -12071,11 +12071,11 @@
       </c>
       <c r="O183" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P183" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="184">
@@ -12133,11 +12133,11 @@
       </c>
       <c r="O184" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P184" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="185">
@@ -12195,11 +12195,11 @@
       </c>
       <c r="O185" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P185" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="186">
@@ -12257,11 +12257,11 @@
       </c>
       <c r="O186" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P186" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="187">
@@ -12319,11 +12319,11 @@
       </c>
       <c r="O187" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P187" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="188">
@@ -12381,11 +12381,11 @@
       </c>
       <c r="O188" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P188" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="189">
@@ -12443,11 +12443,11 @@
       </c>
       <c r="O189" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P189" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="190">
@@ -12505,11 +12505,11 @@
       </c>
       <c r="O190" s="54" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P190" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="191">
@@ -12567,11 +12567,11 @@
       </c>
       <c r="O191" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P191" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="192">
@@ -12629,11 +12629,11 @@
       </c>
       <c r="O192" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P192" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="193">
@@ -12691,11 +12691,11 @@
       </c>
       <c r="O193" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P193" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="194">
@@ -12753,11 +12753,11 @@
       </c>
       <c r="O194" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P194" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="195">
@@ -12815,11 +12815,11 @@
       </c>
       <c r="O195" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P195" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="196">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="H196" s="54" t="inlineStr">
         <is>
-          <t>021-1 BD40 - SM 021 - Digital input</t>
+          <t>021-1BD40 - SM 021 - Digital input</t>
         </is>
       </c>
       <c r="I196" s="54" t="n">
@@ -12877,11 +12877,11 @@
       </c>
       <c r="O196" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P196" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="197">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="H197" s="54" t="inlineStr">
         <is>
-          <t>022-1 B890 - SM 022 - Digital output</t>
+          <t>022-1BB90 - SM 022 - Digital output</t>
         </is>
       </c>
       <c r="I197" s="54" t="n">
@@ -12939,11 +12939,11 @@
       </c>
       <c r="O197" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P197" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="198">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="H198" s="54" t="inlineStr">
         <is>
-          <t>022-1 B890 - SM 022 - Digital output</t>
+          <t>022-1BB90 - SM 022 - Digital output</t>
         </is>
       </c>
       <c r="I198" s="54" t="n">
@@ -13001,11 +13001,11 @@
       </c>
       <c r="O198" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P198" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="199">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="H199" s="54" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="I199" s="54" t="n">
@@ -13063,11 +13063,11 @@
       </c>
       <c r="O199" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P199" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="200">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="H200" s="54" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="I200" s="54" t="n">
@@ -13125,11 +13125,11 @@
       </c>
       <c r="O200" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P200" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="201">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="H201" s="54" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="I201" s="54" t="n">
@@ -13187,11 +13187,11 @@
       </c>
       <c r="O201" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P201" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="202">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="H202" s="54" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="I202" s="54" t="n">
@@ -13249,11 +13249,11 @@
       </c>
       <c r="O202" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P202" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="203">
@@ -13311,11 +13311,11 @@
       </c>
       <c r="O203" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P203" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="204">
@@ -13373,11 +13373,11 @@
       </c>
       <c r="O204" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P204" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="205">
@@ -13435,11 +13435,11 @@
       </c>
       <c r="O205" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P205" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="206">
@@ -13497,11 +13497,11 @@
       </c>
       <c r="O206" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P206" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="207">
@@ -13559,11 +13559,11 @@
       </c>
       <c r="O207" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P207" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="208">
@@ -13621,11 +13621,11 @@
       </c>
       <c r="O208" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P208" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="209">
@@ -13683,11 +13683,11 @@
       </c>
       <c r="O209" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P209" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="210">
@@ -13745,11 +13745,11 @@
       </c>
       <c r="O210" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P210" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="211">
@@ -13807,11 +13807,11 @@
       </c>
       <c r="O211" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P211" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="212">
@@ -13869,11 +13869,11 @@
       </c>
       <c r="O212" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P212" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="213">
@@ -13931,11 +13931,11 @@
       </c>
       <c r="O213" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P213" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="214">
@@ -13993,11 +13993,11 @@
       </c>
       <c r="O214" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P214" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="215">
@@ -14055,11 +14055,11 @@
       </c>
       <c r="O215" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P215" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="216">
@@ -14117,11 +14117,11 @@
       </c>
       <c r="O216" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P216" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="217">
@@ -14179,11 +14179,11 @@
       </c>
       <c r="O217" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P217" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="218">
@@ -14241,11 +14241,11 @@
       </c>
       <c r="O218" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P218" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="219">
@@ -14303,11 +14303,11 @@
       </c>
       <c r="O219" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P219" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="220">
@@ -14365,11 +14365,11 @@
       </c>
       <c r="O220" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P220" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="221">
@@ -14427,11 +14427,11 @@
       </c>
       <c r="O221" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P221" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="222">
@@ -14489,11 +14489,11 @@
       </c>
       <c r="O222" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P222" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="223">
@@ -14551,11 +14551,11 @@
       </c>
       <c r="O223" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P223" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="224">
@@ -14613,11 +14613,11 @@
       </c>
       <c r="O224" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P224" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="225">
@@ -14675,11 +14675,11 @@
       </c>
       <c r="O225" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P225" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="226">
@@ -14737,11 +14737,11 @@
       </c>
       <c r="O226" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P226" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="227">
@@ -14799,11 +14799,11 @@
       </c>
       <c r="O227" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P227" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="228">
@@ -14865,11 +14865,11 @@
       </c>
       <c r="O228" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P228" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="229">
@@ -14931,11 +14931,11 @@
       </c>
       <c r="O229" s="54" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>ses</t>
         </is>
       </c>
       <c r="P229" s="53" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="231">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="G2" s="60" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H2" s="60" t="inlineStr"/>
@@ -15136,7 +15136,7 @@
       </c>
       <c r="G3" s="60" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H3" s="60" t="inlineStr"/>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="G6" s="60" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO000MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H6" s="60" t="inlineStr"/>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="G32" s="60" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00M00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H32" s="60" t="inlineStr"/>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="G33" s="60" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN</t>
+          <t>315-4NE23 - VIPA CPU 315SN</t>
         </is>
       </c>
       <c r="H33" s="60" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="G34" s="60" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN</t>
+          <t>315-4NE23 - VIPA CPU 315SN</t>
         </is>
       </c>
       <c r="H34" s="60" t="inlineStr"/>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="G60" s="60" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-COO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H60" s="60" t="inlineStr"/>
@@ -24794,7 +24794,7 @@
       </c>
       <c r="G196" s="60" t="inlineStr">
         <is>
-          <t>021-1 BD40 - SM 021 - Digital input</t>
+          <t>021-1BD40 - SM 021 - Digital input</t>
         </is>
       </c>
       <c r="H196" s="60" t="inlineStr"/>
@@ -24844,7 +24844,7 @@
       </c>
       <c r="G197" s="60" t="inlineStr">
         <is>
-          <t>022-1 B890 - SM 022 - Digital output</t>
+          <t>022-1BB90 - SM 022 - Digital output</t>
         </is>
       </c>
       <c r="H197" s="60" t="inlineStr"/>
@@ -24894,7 +24894,7 @@
       </c>
       <c r="G198" s="60" t="inlineStr">
         <is>
-          <t>022-1 B890 - SM 022 - Digital output</t>
+          <t>022-1BB90 - SM 022 - Digital output</t>
         </is>
       </c>
       <c r="H198" s="60" t="inlineStr"/>
@@ -24944,7 +24944,7 @@
       </c>
       <c r="G199" s="60" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H199" s="60" t="inlineStr"/>
@@ -24994,7 +24994,7 @@
       </c>
       <c r="G200" s="60" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H200" s="60" t="inlineStr"/>
@@ -25044,7 +25044,7 @@
       </c>
       <c r="G201" s="60" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H201" s="60" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="G202" s="60" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H202" s="60" t="inlineStr"/>
@@ -26502,7 +26502,7 @@
       </c>
       <c r="G230" s="60" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H230" s="60" t="inlineStr"/>
@@ -26552,7 +26552,7 @@
       </c>
       <c r="G231" s="60" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H231" s="60" t="inlineStr"/>
@@ -26710,7 +26710,7 @@
       </c>
       <c r="G234" s="60" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO000MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H234" s="60" t="inlineStr"/>
@@ -28010,7 +28010,7 @@
       </c>
       <c r="G260" s="60" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00M00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H260" s="60" t="inlineStr"/>
@@ -28060,7 +28060,7 @@
       </c>
       <c r="G261" s="60" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN</t>
+          <t>315-4NE23 - VIPA CPU 315SN</t>
         </is>
       </c>
       <c r="H261" s="60" t="inlineStr"/>
@@ -28110,7 +28110,7 @@
       </c>
       <c r="G262" s="60" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN</t>
+          <t>315-4NE23 - VIPA CPU 315SN</t>
         </is>
       </c>
       <c r="H262" s="60" t="inlineStr"/>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="G288" s="60" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-COO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H288" s="60" t="inlineStr"/>
@@ -36210,7 +36210,7 @@
       </c>
       <c r="G424" s="60" t="inlineStr">
         <is>
-          <t>021-1 BD40 - SM 021 - Digital input</t>
+          <t>021-1BD40 - SM 021 - Digital input</t>
         </is>
       </c>
       <c r="H424" s="60" t="inlineStr"/>
@@ -36260,7 +36260,7 @@
       </c>
       <c r="G425" s="60" t="inlineStr">
         <is>
-          <t>022-1 B890 - SM 022 - Digital output</t>
+          <t>022-1BB90 - SM 022 - Digital output</t>
         </is>
       </c>
       <c r="H425" s="60" t="inlineStr"/>
@@ -36310,7 +36310,7 @@
       </c>
       <c r="G426" s="60" t="inlineStr">
         <is>
-          <t>022-1 B890 - SM 022 - Digital output</t>
+          <t>022-1BB90 - SM 022 - Digital output</t>
         </is>
       </c>
       <c r="H426" s="60" t="inlineStr"/>
@@ -36360,7 +36360,7 @@
       </c>
       <c r="G427" s="60" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H427" s="60" t="inlineStr"/>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="G428" s="60" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H428" s="60" t="inlineStr"/>
@@ -36460,7 +36460,7 @@
       </c>
       <c r="G429" s="60" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H429" s="60" t="inlineStr"/>
@@ -36510,7 +36510,7 @@
       </c>
       <c r="G430" s="60" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H430" s="60" t="inlineStr"/>
@@ -39533,7 +39533,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>955-C000M00</t>
+          <t>955-CO00MO00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -39543,14 +39543,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/705</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>955-C000M00</t>
+          <t>955-CO00MO00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -39560,7 +39560,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/705</t>
         </is>
       </c>
     </row>
@@ -39581,7 +39581,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/708</t>
         </is>
       </c>
     </row>
@@ -39602,14 +39602,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/708</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>955-C000M00</t>
+          <t>955-CO000MO00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -39619,14 +39619,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/710</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -39636,14 +39636,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -39653,14 +39653,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -39670,14 +39670,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -39687,14 +39687,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -39704,14 +39704,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -39721,14 +39721,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -39738,14 +39738,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -39755,14 +39755,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -39772,14 +39772,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -39789,14 +39789,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -39806,14 +39806,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -39823,14 +39823,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -39840,14 +39840,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -39857,14 +39857,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -39874,14 +39874,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -39891,14 +39891,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -39908,14 +39908,14 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -39925,14 +39925,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -39942,14 +39942,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -39959,14 +39959,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -39976,14 +39976,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -39993,14 +39993,14 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -40010,14 +40010,14 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -40027,14 +40027,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -40044,14 +40044,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>955-C000M00</t>
+          <t>955-CO00M00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -40061,7 +40061,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
@@ -40078,7 +40078,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/717</t>
         </is>
       </c>
     </row>
@@ -40095,14 +40095,14 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/717</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -40119,7 +40119,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -40136,7 +40136,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -40153,7 +40153,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -40170,7 +40170,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -40187,7 +40187,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -40204,7 +40204,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -40221,7 +40221,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -40238,7 +40238,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -40255,7 +40255,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -40272,7 +40272,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -40289,7 +40289,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -40306,7 +40306,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -40323,7 +40323,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -40340,7 +40340,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -40357,7 +40357,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -40374,7 +40374,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -40391,7 +40391,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -40408,7 +40408,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -40425,7 +40425,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -40442,7 +40442,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -40459,7 +40459,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -40476,7 +40476,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -40493,7 +40493,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -40510,7 +40510,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -40527,7 +40527,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>955-C000M00</t>
+          <t>955-COO00MO00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -40554,7 +40554,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40571,7 +40571,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40588,7 +40588,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40605,7 +40605,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40622,7 +40622,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40639,7 +40639,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40656,7 +40656,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40673,7 +40673,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40690,7 +40690,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40707,7 +40707,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40724,7 +40724,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40741,7 +40741,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40758,7 +40758,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40775,7 +40775,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40792,7 +40792,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40809,7 +40809,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40826,7 +40826,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40843,7 +40843,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40860,7 +40860,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40877,7 +40877,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40894,7 +40894,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40911,7 +40911,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40928,7 +40928,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40945,7 +40945,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40962,7 +40962,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40996,7 +40996,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41013,7 +41013,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41030,7 +41030,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41047,7 +41047,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41064,7 +41064,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41081,7 +41081,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41098,7 +41098,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41115,7 +41115,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41132,7 +41132,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41149,7 +41149,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41166,7 +41166,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41183,7 +41183,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41200,7 +41200,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41217,7 +41217,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41251,7 +41251,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41268,7 +41268,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41285,7 +41285,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41302,7 +41302,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41319,7 +41319,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41336,7 +41336,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41353,7 +41353,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41370,7 +41370,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41387,7 +41387,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41404,7 +41404,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41421,7 +41421,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41438,7 +41438,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41455,7 +41455,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41472,7 +41472,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41489,7 +41489,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41506,7 +41506,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41523,7 +41523,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41540,7 +41540,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41557,7 +41557,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41574,7 +41574,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41591,7 +41591,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41608,7 +41608,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41625,7 +41625,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41642,7 +41642,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41659,7 +41659,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41676,7 +41676,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41693,7 +41693,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41710,7 +41710,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41727,7 +41727,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41744,7 +41744,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41761,7 +41761,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41778,7 +41778,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41795,7 +41795,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41812,7 +41812,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41829,7 +41829,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41846,7 +41846,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41863,7 +41863,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41880,7 +41880,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41897,7 +41897,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41914,7 +41914,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41931,7 +41931,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41948,7 +41948,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41982,7 +41982,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41999,7 +41999,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42016,7 +42016,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42033,7 +42033,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42050,7 +42050,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42067,7 +42067,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42084,7 +42084,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42101,7 +42101,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42118,7 +42118,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42135,7 +42135,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42152,7 +42152,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42169,7 +42169,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42186,7 +42186,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42203,7 +42203,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42220,7 +42220,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42237,7 +42237,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42254,7 +42254,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42271,7 +42271,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42288,7 +42288,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42305,7 +42305,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42339,7 +42339,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42356,7 +42356,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42373,7 +42373,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42390,7 +42390,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42407,7 +42407,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42424,7 +42424,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42441,7 +42441,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42458,7 +42458,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42475,7 +42475,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42492,7 +42492,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42509,7 +42509,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42526,7 +42526,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42543,7 +42543,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42560,7 +42560,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42577,7 +42577,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42594,7 +42594,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42611,7 +42611,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42628,7 +42628,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42645,7 +42645,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42662,7 +42662,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42679,7 +42679,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42696,7 +42696,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42713,7 +42713,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42730,7 +42730,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42747,7 +42747,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42764,7 +42764,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42781,7 +42781,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42798,7 +42798,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42815,7 +42815,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42832,7 +42832,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42849,7 +42849,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42866,7 +42866,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42883,7 +42883,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42900,7 +42900,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42917,7 +42917,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42934,7 +42934,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42951,7 +42951,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42968,7 +42968,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42985,7 +42985,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43002,7 +43002,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43019,7 +43019,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43036,7 +43036,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43053,7 +43053,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43070,7 +43070,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43087,7 +43087,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43104,7 +43104,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43121,7 +43121,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43138,7 +43138,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43155,7 +43155,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43172,7 +43172,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43189,7 +43189,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43206,7 +43206,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43223,7 +43223,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43240,7 +43240,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43257,7 +43257,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43274,7 +43274,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43291,7 +43291,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43308,7 +43308,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43325,7 +43325,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43342,7 +43342,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43359,7 +43359,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43376,7 +43376,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43397,7 +43397,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43418,7 +43418,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>ses</t>
         </is>
       </c>
     </row>
@@ -43438,7 +43438,7 @@
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -43698,7 +43698,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0 items from OCR</t>
+          <t>228 items from OCR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -43784,7 +43784,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -43799,7 +43799,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -43821,7 +43821,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -43836,7 +43836,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -43873,7 +43873,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -43910,7 +43910,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -43932,7 +43932,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
+          <t>955-CO000MO00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -43947,7 +43947,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -43984,7 +43984,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44021,7 +44021,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44095,7 +44095,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44132,7 +44132,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44169,7 +44169,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44206,7 +44206,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44243,7 +44243,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44280,7 +44280,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44317,7 +44317,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44354,7 +44354,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44391,7 +44391,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44428,7 +44428,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44465,7 +44465,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44502,7 +44502,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44539,7 +44539,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44576,7 +44576,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44613,7 +44613,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44650,7 +44650,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44687,7 +44687,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44724,7 +44724,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44761,7 +44761,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44798,7 +44798,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44835,7 +44835,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44872,7 +44872,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44894,7 +44894,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
+          <t>955-CO00M00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -44909,7 +44909,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44931,7 +44931,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN (Qty=1, Tot=126780.98)</t>
+          <t>315-4NE23 - VIPA CPU 315SN (Qty=1, Tot=126780.98)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -44946,7 +44946,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN (Qty=1, Tot=126780.97)</t>
+          <t>315-4NE23 - VIPA CPU 315SN (Qty=1, Tot=126780.97)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -44983,7 +44983,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45020,7 +45020,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45057,7 +45057,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45094,7 +45094,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45131,7 +45131,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45168,7 +45168,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45205,7 +45205,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45242,7 +45242,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45279,7 +45279,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45316,7 +45316,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45390,7 +45390,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45427,7 +45427,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45464,7 +45464,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45501,7 +45501,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45538,7 +45538,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45575,7 +45575,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45612,7 +45612,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45649,7 +45649,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45686,7 +45686,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45723,7 +45723,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45760,7 +45760,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45797,7 +45797,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45834,7 +45834,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45871,7 +45871,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45908,7 +45908,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45930,7 +45930,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
+          <t>955-COO00MO00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -45945,7 +45945,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45982,7 +45982,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46019,7 +46019,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46056,7 +46056,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46093,7 +46093,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46130,7 +46130,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46167,7 +46167,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46204,7 +46204,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46241,7 +46241,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46278,7 +46278,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46315,7 +46315,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46352,7 +46352,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46389,7 +46389,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46426,7 +46426,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46463,7 +46463,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46500,7 +46500,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46537,7 +46537,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46574,7 +46574,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46611,7 +46611,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46648,7 +46648,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46685,7 +46685,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46722,7 +46722,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46759,7 +46759,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46796,7 +46796,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46833,7 +46833,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46870,7 +46870,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46907,7 +46907,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46944,7 +46944,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46981,7 +46981,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47018,7 +47018,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47055,7 +47055,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47092,7 +47092,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47129,7 +47129,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47166,7 +47166,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47203,7 +47203,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47240,7 +47240,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47277,7 +47277,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47314,7 +47314,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47351,7 +47351,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47388,7 +47388,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47462,7 +47462,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
